--- a/outputs/daily/hr_rankings_2026-08-07_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-07_full.xlsx
@@ -68835,27 +68835,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>700337</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Edgar Quero</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-08-07T22:45:00Z</t>
+          <t>2026-08-07T23:40:00Z</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -68870,21 +68870,21 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L252" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
@@ -68902,22 +68902,22 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>8.699999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="Q252" t="n">
-        <v>31.5</v>
+        <v>17.8</v>
       </c>
       <c r="R252" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S252" t="n">
         <v>47.9</v>
       </c>
       <c r="T252" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U252" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
@@ -68956,7 +68956,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr"/>
@@ -68968,32 +68968,32 @@
       </c>
       <c r="AG252" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Last 2 games: 0/5, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
@@ -69003,104 +69003,104 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>85.9599</t>
+          <t>99.0634</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.3201</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.0953</t>
         </is>
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.2746</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.48</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0551</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="BD252" t="inlineStr">
         <is>
-          <t>0.3825</t>
+          <t>0.3442</t>
         </is>
       </c>
       <c r="BE252" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BG252" t="inlineStr"/>
       <c r="BH252" t="inlineStr"/>
       <c r="BI252" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ252" t="inlineStr"/>
@@ -69111,24 +69111,24 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="F253" t="inlineStr">
         <is>
           <t>2026-08-07T22:45:00Z</t>
@@ -69144,9 +69144,21 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>676917</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L253" t="n">
         <v>28.6</v>
       </c>
@@ -69162,14 +69174,14 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P253" t="n">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q253" t="n">
-        <v>41.2</v>
+        <v>31.5</v>
       </c>
       <c r="R253" t="n">
         <v>28.2</v>
@@ -69178,10 +69190,10 @@
         <v>47.9</v>
       </c>
       <c r="T253" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U253" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
@@ -69220,7 +69232,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr"/>
@@ -69232,17 +69244,17 @@
       </c>
       <c r="AG253" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
@@ -69252,12 +69264,12 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 2 games: 0/5, 0 HR</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
@@ -69267,75 +69279,99 @@
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>95.4872</t>
+          <t>85.9599</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>0.3247</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>0.0806</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>0.2996</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>0.0904</t>
-        </is>
-      </c>
-      <c r="BA253" t="inlineStr"/>
-      <c r="BB253" t="inlineStr"/>
-      <c r="BC253" t="inlineStr"/>
-      <c r="BD253" t="inlineStr"/>
-      <c r="BE253" t="inlineStr"/>
-      <c r="BF253" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>41.24</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>88.82</t>
+        </is>
+      </c>
+      <c r="BD253" t="inlineStr">
+        <is>
+          <t>0.3825</t>
+        </is>
+      </c>
+      <c r="BE253" t="inlineStr">
+        <is>
+          <t>0.1312</t>
+        </is>
+      </c>
+      <c r="BF253" t="inlineStr">
+        <is>
+          <t>20.84</t>
+        </is>
+      </c>
       <c r="BG253" t="inlineStr"/>
       <c r="BH253" t="inlineStr"/>
       <c r="BI253" t="inlineStr">
@@ -69351,27 +69387,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-08T02:15:00Z</t>
+          <t>2026-08-07T22:45:00Z</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -69381,14 +69417,14 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -69406,22 +69442,22 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q254" t="n">
         <v>41.2</v>
       </c>
       <c r="R254" t="n">
-        <v>19.3</v>
+        <v>28.2</v>
       </c>
       <c r="S254" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T254" t="n">
         <v>60</v>
       </c>
       <c r="U254" t="n">
-        <v>34.5</v>
+        <v>10.1</v>
       </c>
       <c r="V254" t="inlineStr">
         <is>
@@ -69435,7 +69471,7 @@
       </c>
       <c r="X254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y254" t="inlineStr">
@@ -69477,12 +69513,12 @@
       </c>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ254" t="inlineStr">
@@ -69492,7 +69528,7 @@
       </c>
       <c r="AK254" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL254" t="inlineStr">
@@ -69507,67 +69543,67 @@
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>85.56</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>95.9699</t>
+          <t>95.4872</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3247</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.0806</t>
         </is>
       </c>
       <c r="AT254" t="inlineStr">
         <is>
-          <t>0.2938</t>
+          <t>0.2996</t>
         </is>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>68.13</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>0.1307</t>
+          <t>0.0904</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr"/>
@@ -69580,7 +69616,7 @@
       <c r="BH254" t="inlineStr"/>
       <c r="BI254" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ254" t="inlineStr"/>
@@ -69591,27 +69627,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-08-08T00:15:00Z</t>
+          <t>2026-08-08T02:15:00Z</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -69624,23 +69660,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>Shane Baz</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>669358</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -69654,26 +69678,26 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P255" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q255" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R255" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S255" t="n">
         <v>40.2</v>
       </c>
       <c r="T255" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U255" t="n">
-        <v>2.5</v>
+        <v>34.5</v>
       </c>
       <c r="V255" t="inlineStr">
         <is>
@@ -69712,7 +69736,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr"/>
@@ -69729,12 +69753,12 @@
       </c>
       <c r="AH255" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ255" t="inlineStr">
@@ -69744,12 +69768,12 @@
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL255" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 14.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
@@ -69759,104 +69783,80 @@
       </c>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>85.56</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>95.3325</t>
+          <t>95.9699</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
         <is>
-          <t>0.2669</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>0.0405</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="AT255" t="inlineStr">
         <is>
-          <t>0.2568</t>
+          <t>0.2938</t>
         </is>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>68.13</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>0.0238</t>
-        </is>
-      </c>
-      <c r="BA255" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="BB255" t="inlineStr">
-        <is>
-          <t>41.29</t>
-        </is>
-      </c>
-      <c r="BC255" t="inlineStr">
-        <is>
-          <t>89.98</t>
-        </is>
-      </c>
-      <c r="BD255" t="inlineStr">
-        <is>
-          <t>0.3993</t>
-        </is>
-      </c>
-      <c r="BE255" t="inlineStr">
-        <is>
-          <t>0.1476</t>
-        </is>
-      </c>
-      <c r="BF255" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
+          <t>0.1307</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr"/>
+      <c r="BB255" t="inlineStr"/>
+      <c r="BC255" t="inlineStr"/>
+      <c r="BD255" t="inlineStr"/>
+      <c r="BE255" t="inlineStr"/>
+      <c r="BF255" t="inlineStr"/>
       <c r="BG255" t="inlineStr"/>
       <c r="BH255" t="inlineStr"/>
       <c r="BI255" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ255" t="inlineStr"/>
@@ -69867,27 +69867,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>680716</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Jonathan Ornelas</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-08-07T23:10:00Z</t>
+          <t>2026-08-08T00:15:00Z</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -69902,21 +69902,21 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>669358</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L256" t="n">
-        <v>27.1</v>
+        <v>27.5</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -69934,22 +69934,22 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q256" t="n">
-        <v>30.8</v>
+        <v>40.1</v>
       </c>
       <c r="R256" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S256" t="n">
         <v>40.2</v>
       </c>
       <c r="T256" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U256" t="n">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="V256" t="inlineStr">
         <is>
@@ -70000,17 +70000,17 @@
       </c>
       <c r="AG256" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI256" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ256" t="inlineStr">
@@ -70020,12 +70020,12 @@
       </c>
       <c r="AK256" t="inlineStr">
         <is>
-          <t>Last 4 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL256" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM256" t="inlineStr">
@@ -70040,99 +70040,99 @@
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>84.56</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>95.008</t>
+          <t>95.3325</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.2669</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>0.0099</t>
+          <t>0.0405</t>
         </is>
       </c>
       <c r="AT256" t="inlineStr">
         <is>
-          <t>0.1724</t>
+          <t>0.2568</t>
         </is>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>33.53</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>57.51</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0238</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="BD256" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE256" t="inlineStr">
         <is>
-          <t>0.1394</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG256" t="inlineStr"/>
       <c r="BH256" t="inlineStr"/>
       <c r="BI256" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ256" t="inlineStr"/>
@@ -70143,27 +70143,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>680716</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Jonathan Ornelas</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-07T22:40:00Z</t>
+          <t>2026-08-07T23:10:00Z</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -70173,26 +70173,26 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L257" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -70206,26 +70206,26 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P257" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q257" t="n">
-        <v>23.5</v>
+        <v>30.8</v>
       </c>
       <c r="R257" t="n">
-        <v>34.3</v>
+        <v>28.7</v>
       </c>
       <c r="S257" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T257" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U257" t="n">
-        <v>24.3</v>
+        <v>19.5</v>
       </c>
       <c r="V257" t="inlineStr">
         <is>
@@ -70239,7 +70239,7 @@
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
@@ -70276,32 +70276,32 @@
       </c>
       <c r="AG257" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 4 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL257" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
@@ -70311,104 +70311,104 @@
       </c>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>22.64</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>85.41</t>
+          <t>84.56</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>94.8236</t>
+          <t>95.008</t>
         </is>
       </c>
       <c r="AR257" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>0.0902</t>
+          <t>0.0099</t>
         </is>
       </c>
       <c r="AT257" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.1724</t>
         </is>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>33.53</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>57.51</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>0.1259</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD257" t="inlineStr">
         <is>
-          <t>0.3123</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="BE257" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.1394</t>
         </is>
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="BG257" t="inlineStr"/>
       <c r="BH257" t="inlineStr"/>
       <c r="BI257" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ257" t="inlineStr"/>
@@ -70419,27 +70419,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-08-07T23:40:00Z</t>
+          <t>2026-08-07T22:40:00Z</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -70449,22 +70449,22 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -70482,26 +70482,26 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P258" t="n">
-        <v>15</v>
+        <v>6.3</v>
       </c>
       <c r="Q258" t="n">
-        <v>18.7</v>
+        <v>23.5</v>
       </c>
       <c r="R258" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S258" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T258" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U258" t="n">
-        <v>14.1</v>
+        <v>24.3</v>
       </c>
       <c r="V258" t="inlineStr">
         <is>
@@ -70515,7 +70515,7 @@
       </c>
       <c r="X258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y258" t="inlineStr">
@@ -70557,27 +70557,27 @@
       </c>
       <c r="AH258" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI258" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL258" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM258" t="inlineStr">
@@ -70587,104 +70587,104 @@
       </c>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>22.64</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>85.41</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>99.5629</t>
+          <t>94.8236</t>
         </is>
       </c>
       <c r="AR258" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.0902</t>
         </is>
       </c>
       <c r="AT258" t="inlineStr">
         <is>
-          <t>0.2738</t>
+          <t>0.2771</t>
         </is>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>0.0365</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="BD258" t="inlineStr">
         <is>
-          <t>0.3442</t>
+          <t>0.3123</t>
         </is>
       </c>
       <c r="BE258" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="BG258" t="inlineStr"/>
       <c r="BH258" t="inlineStr"/>
       <c r="BI258" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ258" t="inlineStr"/>
@@ -70695,27 +70695,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>664702</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-08-07T22:40:00Z</t>
+          <t>2026-08-07T23:40:00Z</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -70730,21 +70730,21 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L259" t="n">
-        <v>25.8</v>
+        <v>26.9</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
@@ -70758,26 +70758,26 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P259" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q259" t="n">
-        <v>23.5</v>
+        <v>18.7</v>
       </c>
       <c r="R259" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S259" t="n">
         <v>40.2</v>
       </c>
       <c r="T259" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U259" t="n">
-        <v>24.9</v>
+        <v>14.1</v>
       </c>
       <c r="V259" t="inlineStr">
         <is>
@@ -70833,12 +70833,12 @@
       </c>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI259" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ259" t="inlineStr">
@@ -70848,12 +70848,12 @@
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL259" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
@@ -70863,104 +70863,104 @@
       </c>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>86.43</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>96.0047</t>
+          <t>99.5629</t>
         </is>
       </c>
       <c r="AR259" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="AT259" t="inlineStr">
         <is>
-          <t>0.2978</t>
+          <t>0.2738</t>
         </is>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>68.26</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>32.92</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.0365</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="BD259" t="inlineStr">
         <is>
-          <t>0.3123</t>
+          <t>0.3442</t>
         </is>
       </c>
       <c r="BE259" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BG259" t="inlineStr"/>
       <c r="BH259" t="inlineStr"/>
       <c r="BI259" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ259" t="inlineStr"/>
@@ -70971,27 +70971,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>664702</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2026-08-07T23:40:00Z</t>
+          <t>2026-08-07T22:40:00Z</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -71001,60 +71001,60 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L260" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Projected Lineup</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R260" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="S260" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="T260" t="n">
+        <v>50</v>
+      </c>
+      <c r="U260" t="n">
         <v>24.9</v>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O260" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P260" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q260" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="R260" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S260" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="T260" t="n">
-        <v>75</v>
-      </c>
-      <c r="U260" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V260" t="inlineStr">
         <is>
           <t>No</t>
@@ -71067,7 +71067,7 @@
       </c>
       <c r="X260" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y260" t="inlineStr">
@@ -71109,7 +71109,7 @@
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI260" t="inlineStr">
@@ -71124,12 +71124,12 @@
       </c>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL260" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM260" t="inlineStr">
@@ -71139,104 +71139,104 @@
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>86.43</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>94.8593</t>
+          <t>96.0047</t>
         </is>
       </c>
       <c r="AR260" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>0.0693</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="AT260" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.2978</t>
         </is>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.26</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="BD260" t="inlineStr">
         <is>
-          <t>0.3442</t>
+          <t>0.3123</t>
         </is>
       </c>
       <c r="BE260" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="BG260" t="inlineStr"/>
       <c r="BH260" t="inlineStr"/>
       <c r="BI260" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ260" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-07_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-07_full.xlsx
@@ -43731,27 +43731,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>681198</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-07T23:10:00Z</t>
+          <t>2026-08-08T00:15:00Z</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -43761,17 +43761,17 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>681517</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -43780,7 +43780,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -43794,26 +43794,26 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>30.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q160" t="n">
-        <v>39</v>
+        <v>54.1</v>
       </c>
       <c r="R160" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="S160" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T160" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U160" t="n">
-        <v>16.6</v>
+        <v>20.9</v>
       </c>
       <c r="V160" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
@@ -43869,12 +43869,12 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
@@ -43884,12 +43884,12 @@
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
@@ -43899,104 +43899,104 @@
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>99.6179</t>
+          <t>96.3314</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.78</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>0.4008</t>
+          <t>0.4475</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr"/>
       <c r="BH160" t="inlineStr"/>
       <c r="BI160" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ160" t="inlineStr"/>
@@ -44007,12 +44007,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>681198</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -44037,7 +44037,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -44070,11 +44070,11 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>12.8</v>
+        <v>23.8</v>
       </c>
       <c r="Q161" t="n">
         <v>54.1</v>
@@ -44083,13 +44083,13 @@
         <v>22.1</v>
       </c>
       <c r="S161" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T161" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U161" t="n">
-        <v>20.9</v>
+        <v>32</v>
       </c>
       <c r="V161" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -44128,7 +44128,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr"/>
@@ -44145,12 +44145,12 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
@@ -44160,12 +44160,12 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -44175,67 +44175,67 @@
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>96.3314</t>
+          <t>99.6251</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.1166</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1252</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
@@ -44283,27 +44283,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-08T00:15:00Z</t>
+          <t>2026-08-07T23:10:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -44313,17 +44313,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>681517</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -44332,7 +44332,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -44346,26 +44346,26 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>23.8</v>
+        <v>30.1</v>
       </c>
       <c r="Q162" t="n">
-        <v>54.1</v>
+        <v>39</v>
       </c>
       <c r="R162" t="n">
-        <v>22.1</v>
+        <v>21.5</v>
       </c>
       <c r="S162" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>32</v>
+        <v>10.8</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr"/>
@@ -44421,12 +44421,12 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -44436,12 +44436,12 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.1 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -44451,104 +44451,104 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>99.6251</t>
+          <t>99.6179</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.1166</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>90.78</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.4475</t>
+          <t>0.4008</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr"/>
       <c r="BH162" t="inlineStr"/>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
